--- a/artfynd/A 6909-2026 artfynd.xlsx
+++ b/artfynd/A 6909-2026 artfynd.xlsx
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131661937</v>
+        <v>131661951</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,23 +1603,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499266</v>
+        <v>499727</v>
       </c>
       <c r="R11" t="n">
-        <v>7085681</v>
+        <v>7085643</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,11 +1659,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131661951</v>
+        <v>131661937</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,19 +1696,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1725,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499727</v>
+        <v>499266</v>
       </c>
       <c r="R12" t="n">
-        <v>7085643</v>
+        <v>7085681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131661946</v>
+        <v>131661944</v>
       </c>
       <c r="B14" t="n">
         <v>57898</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499692</v>
+        <v>499509</v>
       </c>
       <c r="R14" t="n">
-        <v>7085658</v>
+        <v>7085596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131661944</v>
+        <v>131661946</v>
       </c>
       <c r="B15" t="n">
         <v>57898</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499509</v>
+        <v>499692</v>
       </c>
       <c r="R15" t="n">
-        <v>7085596</v>
+        <v>7085658</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 6909-2026 artfynd.xlsx
+++ b/artfynd/A 6909-2026 artfynd.xlsx
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131661952</v>
+        <v>131661944</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499319</v>
+        <v>499509</v>
       </c>
       <c r="R13" t="n">
-        <v>7085668</v>
+        <v>7085596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131661944</v>
+        <v>131661946</v>
       </c>
       <c r="B14" t="n">
         <v>57898</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499509</v>
+        <v>499692</v>
       </c>
       <c r="R14" t="n">
-        <v>7085596</v>
+        <v>7085658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131661946</v>
+        <v>131661945</v>
       </c>
       <c r="B15" t="n">
         <v>57898</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499692</v>
+        <v>499659</v>
       </c>
       <c r="R15" t="n">
-        <v>7085658</v>
+        <v>7085609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131661945</v>
+        <v>131661952</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2104,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499659</v>
+        <v>499319</v>
       </c>
       <c r="R16" t="n">
-        <v>7085609</v>
+        <v>7085668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 6909-2026 artfynd.xlsx
+++ b/artfynd/A 6909-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131661950</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131661940</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131661947</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131661954</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>131661943</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>131661942</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131661938</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>131661941</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>131661936</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131661951</v>
       </c>
       <c r="B11" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131661937</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131661944</v>
+        <v>131661952</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499509</v>
+        <v>499319</v>
       </c>
       <c r="R13" t="n">
-        <v>7085596</v>
+        <v>7085668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131661946</v>
+        <v>131661944</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499692</v>
+        <v>499509</v>
       </c>
       <c r="R14" t="n">
-        <v>7085658</v>
+        <v>7085596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131661945</v>
+        <v>131661946</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499659</v>
+        <v>499692</v>
       </c>
       <c r="R15" t="n">
-        <v>7085609</v>
+        <v>7085658</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131661952</v>
+        <v>131661945</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2104,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499319</v>
+        <v>499659</v>
       </c>
       <c r="R16" t="n">
-        <v>7085668</v>
+        <v>7085609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 6909-2026 artfynd.xlsx
+++ b/artfynd/A 6909-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131661950</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131661940</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131661947</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131661954</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>131661943</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>131661942</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131661938</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>131661941</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>131661936</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131661951</v>
+        <v>131661937</v>
       </c>
       <c r="B11" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,19 +1603,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1623,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499727</v>
+        <v>499266</v>
       </c>
       <c r="R11" t="n">
-        <v>7085643</v>
+        <v>7085681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,6 +1663,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131661937</v>
+        <v>131661951</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,23 +1705,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1720,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499266</v>
+        <v>499727</v>
       </c>
       <c r="R12" t="n">
-        <v>7085681</v>
+        <v>7085643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1761,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1790,7 @@
         <v>131661952</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>131661944</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>131661946</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>131661945</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
